--- a/output/pdf_financials_xlsx/HXC.H.xlsx
+++ b/output/pdf_financials_xlsx/HXC.H.xlsx
@@ -1251,10 +1251,10 @@
         <v>-0.159978</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.102701</v>
+        <v>-0.102701</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.045603</v>
+        <v>-0.045603</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.037651</v>
+        <v>-0.037651</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.041697</v>
+        <v>-0.041697</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.043104</v>
+        <v>-0.043104</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.03994</v>
+        <v>-0.03994</v>
       </c>
     </row>
     <row r="17">
@@ -1527,10 +1527,10 @@
         <v>-0.159978</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.102701</v>
+        <v>-0.102701</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.045603</v>
+        <v>-0.045603</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1538,16 +1538,16 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.037651</v>
+        <v>-0.037651</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.041697</v>
+        <v>-0.041697</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.043104</v>
+        <v>-0.043104</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.03994</v>
+        <v>-0.03994</v>
       </c>
     </row>
     <row r="21">
@@ -1693,10 +1693,10 @@
         <v>-0.159978</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.102701</v>
+        <v>-0.102701</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.045603</v>
+        <v>-0.045603</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1704,16 +1704,16 @@
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.037651</v>
+        <v>-0.037651</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.041697</v>
+        <v>-0.041697</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.043104</v>
+        <v>-0.043104</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.03994</v>
+        <v>-0.03994</v>
       </c>
     </row>
     <row r="24">
@@ -1937,10 +1937,10 @@
         <v>-0.159978</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.102701</v>
+        <v>-0.102701</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.045603</v>
+        <v>-0.045603</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -1948,16 +1948,16 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.037651</v>
+        <v>-0.037651</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.041697</v>
+        <v>-0.041697</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.043104</v>
+        <v>-0.043104</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.03994</v>
+        <v>-0.03994</v>
       </c>
     </row>
     <row r="28">
@@ -2049,10 +2049,10 @@
         <v>-0.159978</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.102701</v>
+        <v>-0.102701</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.045603</v>
+        <v>-0.045603</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.037651</v>
+        <v>-0.037651</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.041697</v>
+        <v>-0.041697</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.043104</v>
+        <v>-0.043104</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.03994</v>
+        <v>-0.03994</v>
       </c>
     </row>
     <row r="30">
@@ -2187,10 +2187,10 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="1" t="inlineStr">
         <is>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -19043,10 +19043,10 @@
         <v>-0.159978</v>
       </c>
       <c r="M128" s="5" t="n">
-        <v>0.102701</v>
+        <v>-0.102701</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>0.045603</v>
+        <v>-0.045603</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -19054,16 +19054,16 @@
         </is>
       </c>
       <c r="P128" s="5" t="n">
-        <v>0.037651</v>
+        <v>-0.037651</v>
       </c>
       <c r="Q128" s="5" t="n">
-        <v>0.041697</v>
+        <v>-0.041697</v>
       </c>
       <c r="R128" s="5" t="n">
-        <v>0.043104</v>
+        <v>-0.043104</v>
       </c>
       <c r="S128" s="5" t="n">
-        <v>0.03994</v>
+        <v>-0.03994</v>
       </c>
     </row>
     <row r="129">

--- a/output/pdf_financials_xlsx/HXC.H.xlsx
+++ b/output/pdf_financials_xlsx/HXC.H.xlsx
@@ -1004,13 +1004,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000109</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1914,13 +1914,13 @@
         <v>-0.020967</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.073493</v>
+        <v>-0.073602</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.054939</v>
+        <v>-0.054941</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.139259</v>
+        <v>-0.139262</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2026,13 +2026,13 @@
         <v>-0.020967</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.073493</v>
+        <v>-0.073602</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.054939</v>
+        <v>-0.054941</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.139259</v>
+        <v>-0.139262</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.058349</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.346637</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.308862</v>
@@ -2318,7 +2318,7 @@
         <v>0.382954</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.307371</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.245985</v>
@@ -2330,25 +2330,25 @@
         <v>0.04309</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.062087</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.098315</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.022382</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.002388</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.001574</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.00073</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.001161</v>
       </c>
     </row>
     <row r="35">
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.058349</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.346637</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.308862</v>
@@ -2422,7 +2422,7 @@
         <v>0.382954</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.307371</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.245985</v>
@@ -2434,25 +2434,25 @@
         <v>0.04309</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.062087</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.098315</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.022382</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.002388</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.001574</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.00073</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.001161</v>
       </c>
     </row>
     <row r="37">
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.058349</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.346637</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
         <v>0.003874</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.307371</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -3058,25 +3058,25 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.062087</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.098315</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.022382</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.002418</v>
+        <v>3e-05</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.001574</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.00073</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.001161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">

--- a/output/pdf_financials_xlsx/HXC.H.xlsx
+++ b/output/pdf_financials_xlsx/HXC.H.xlsx
@@ -564,10 +564,8 @@
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -584,10 +582,8 @@
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
@@ -620,10 +616,8 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -640,10 +634,8 @@
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
@@ -676,10 +668,8 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -696,10 +686,8 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
@@ -721,53 +709,49 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.009634999999999999</v>
+        <v>0.01224</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.027034</v>
+        <v>0.029802</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.034454</v>
+        <v>0.035441</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.075364</v>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.078134</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.065016</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.042264</v>
+        <v>0.045544</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.043145</v>
+        <v>0.051584</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.03487</v>
+        <v>0.038622</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.032849</v>
+        <v>0.034836</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.028538</v>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.030736</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.025809</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.023777</v>
+        <v>0.025881</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.027135</v>
+        <v>0.029277</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.023558</v>
+        <v>0.025933</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.022953</v>
+        <v>0.025323</v>
       </c>
     </row>
     <row r="8">
@@ -788,10 +772,8 @@
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -808,10 +790,8 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>0</v>
@@ -844,10 +824,8 @@
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -864,10 +842,8 @@
       <c r="K9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>0</v>
@@ -900,10 +876,8 @@
       <c r="E10" s="3" t="n">
         <v>0.139262</v>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F10" s="3" t="n">
+        <v>0.09288200000000001</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.056844</v>
@@ -912,18 +886,16 @@
         <v>0.09148100000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.03487</v>
+        <v>0.038622</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.032849</v>
+        <v>0.034836</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.028538</v>
-      </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.030736</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.025809</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.037651</v>
@@ -956,10 +928,8 @@
       <c r="E11" s="3" t="n">
         <v>-0.139262</v>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="3" t="n">
+        <v>-0.09288200000000001</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.056844</v>
@@ -968,18 +938,16 @@
         <v>-0.09148100000000001</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.03487</v>
+        <v>-0.038622</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.032849</v>
+        <v>-0.034836</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.028538</v>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.030736</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-0.025809</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>-0.037651</v>
@@ -1012,10 +980,8 @@
       <c r="E12" s="3" t="n">
         <v>3e-06</v>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1032,10 +998,8 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1068,10 +1032,8 @@
       <c r="E13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -1088,10 +1050,8 @@
       <c r="K13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>-0</v>
@@ -1124,10 +1084,8 @@
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -1144,10 +1102,8 @@
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0</v>
@@ -1180,10 +1136,8 @@
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -1200,10 +1154,8 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0</v>
@@ -1236,10 +1188,8 @@
       <c r="E16" s="3" t="n">
         <v>-0.139259</v>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="3" t="n">
+        <v>-0.09288200000000001</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.102844</v>
@@ -1256,10 +1206,8 @@
       <c r="K16" s="3" t="n">
         <v>-0.045603</v>
       </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L16" s="3" t="n">
+        <v>-0.038509</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-0.037651</v>
@@ -1292,10 +1240,8 @@
       <c r="E17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1312,10 +1258,8 @@
       <c r="K17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1512,10 +1456,8 @@
       <c r="E20" s="3" t="n">
         <v>-0.139259</v>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F20" s="3" t="n">
+        <v>-0.09288200000000001</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.102844</v>
@@ -1532,10 +1474,8 @@
       <c r="K20" s="3" t="n">
         <v>-0.045603</v>
       </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L20" s="3" t="n">
+        <v>-0.038509</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.037651</v>
@@ -1568,10 +1508,8 @@
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1588,10 +1526,8 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -1624,10 +1560,8 @@
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0</v>
@@ -1644,10 +1578,8 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
@@ -1698,10 +1630,8 @@
       <c r="K23" s="3" t="n">
         <v>-0.045603</v>
       </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L23" s="3" t="n">
+        <v>-0.038509</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-0.037651</v>
@@ -1734,10 +1664,8 @@
       <c r="E24" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F24" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>-0.01</v>
@@ -1754,10 +1682,8 @@
       <c r="K24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>0</v>
@@ -1790,10 +1716,8 @@
       <c r="E25" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F25" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>-0.01</v>
@@ -1810,10 +1734,8 @@
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>0</v>
@@ -1922,10 +1844,8 @@
       <c r="E27" s="3" t="n">
         <v>-0.139262</v>
       </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="3" t="n">
+        <v>-0.09288200000000001</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.102844</v>
@@ -1942,10 +1862,8 @@
       <c r="K27" s="3" t="n">
         <v>-0.045603</v>
       </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L27" s="3" t="n">
+        <v>-0.038509</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.037651</v>
@@ -1978,10 +1896,8 @@
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -1998,10 +1914,8 @@
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0</v>
@@ -2034,10 +1948,8 @@
       <c r="E29" s="3" t="n">
         <v>-0.139262</v>
       </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F29" s="3" t="n">
+        <v>-0.09288200000000001</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.102844</v>
@@ -2054,10 +1966,8 @@
       <c r="K29" s="3" t="n">
         <v>-0.045603</v>
       </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L29" s="3" t="n">
+        <v>-0.038509</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.037651</v>
@@ -2172,10 +2082,8 @@
       <c r="E31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -2192,10 +2100,8 @@
       <c r="K31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -5913,10 +5819,10 @@
         <v>0</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.002762</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000771</v>
       </c>
       <c r="L101" s="1" t="inlineStr">
         <is>
@@ -5924,16 +5830,16 @@
         </is>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.000724</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.001443</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00163</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>0.001072</v>
       </c>
     </row>
     <row r="102">
@@ -6183,10 +6089,10 @@
         <v>-0.004718</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.003036</v>
+        <v>0.005798</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.017398</v>
+        <v>-0.018169</v>
       </c>
       <c r="L106" s="1" t="inlineStr">
         <is>
@@ -6194,16 +6100,16 @@
         </is>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.016933</v>
+        <v>0.017657</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.03944</v>
+        <v>0.040883</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-0.00261</v>
+        <v>-0.00424</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.010701</v>
+        <v>-0.009629</v>
       </c>
     </row>
     <row r="107">
@@ -7847,7 +7753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S177"/>
+  <dimension ref="A1:S181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12441,7 +12347,11 @@
           <t>GST receivables</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -13738,7 +13648,11 @@
           <t>GST receivables 724</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -15854,13 +15768,21 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Net cash flows used in operating activities</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>October 31, 2013 October</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Net cash flows used in operating activities total</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -15872,15 +15794,13 @@
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.002012</v>
+        <v>-0.037775</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.139009</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>-0.075583</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -15941,17 +15861,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Net cash flows used in operating activities</t>
+          <t>CASH FLOWS FROM (USED IN) INVESTMENT ACTIVITIES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Net cash flows used in operating activities total</t>
+          <t>Exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -15964,11 +15884,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G94" s="5" t="n">
-        <v>-0.037775</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>-0.139009</v>
+        <v>-0.03</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -16039,14 +15961,10 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Net cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -16129,12 +16047,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (USED IN) INVESTMENT ACTIVITIES</t>
+          <t>CASH FLOWS FROM (USED IN) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Net cash flows from (used in) investing activities</t>
+          <t>Share issuance for cash</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -16143,10 +16061,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F96" s="5" t="n">
+        <v>0.39161</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -16154,7 +16070,7 @@
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>-0.03</v>
+        <v>0.25</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -16225,17 +16141,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Share issuance for cash</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Share issuance cost</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.39161</v>
+        <v>-0.075292</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -16243,7 +16163,7 @@
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>0.25</v>
+        <v>-0.006899</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -16309,17 +16229,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (USED IN) FINANCING ACTIVITIES</t>
+          <t>243,101</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Share issuance cost</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -16327,8 +16247,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>-0.075292</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -16336,12 +16258,10 @@
         </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.006899</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07409200000000001</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>-0.075583</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -16402,22 +16322,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (USED IN) FINANCING ACTIVITIES</t>
+          <t>243,101</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Net cash flows from (used in) financing activities</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F99" s="5" t="n">
-        <v>0.336618</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -16425,12 +16351,10 @@
         </is>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.243101</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.308862</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0.382954</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -16491,17 +16415,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM (USED IN) FINANCING ACTIVITIES</t>
+          <t>243,101</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chang in cash and cash equivalents</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -16514,16 +16438,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G100" s="5" t="n">
-        <v>-0.037775</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H100" s="5" t="n">
-        <v>0.07409200000000001</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.382954</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>0.307371</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -16582,21 +16506,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>CASH FLOWS FROM (USED IN) FINANCING ACTIVITIES</t>
-        </is>
-      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>October 31, 2013 October</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -16608,10 +16524,10 @@
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.346637</v>
+        <v>0.002012</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>0.308862</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -16682,29 +16598,25 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Net cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>0.308862</v>
+      <c r="F102" s="5" t="n">
+        <v>0.336618</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0.382954</v>
+        <v>0.243101</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -16768,28 +16680,36 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM (USED IN) FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>October 31, 2012 October</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Chang in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F103" s="5" t="n">
-        <v>0.002011</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.037775</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.07409200000000001</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -16860,12 +16780,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Agent’s options exercise for issuance of common shares</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -16873,18 +16793,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F104" s="5" t="n">
-        <v>0.0203</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.346637</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>0.308862</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -16955,12 +16873,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
+          <t>Cash and cash equivalents, end of year $</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -16968,16 +16886,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n">
-        <v>0.288288</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>-0.037775</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.308862</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>0.382954</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -17041,31 +16959,23 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>CASH FLOWS FROM (USED IN) FINANCING ACTIVITIES</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>October 31, 2012 October</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.058349</v>
+        <v>0.002011</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.346637</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17141,12 +17051,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Agent’s options exercise for issuance of common shares</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -17155,10 +17065,12 @@
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.346637</v>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>0.308862</v>
+        <v>0.0203</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17229,29 +17141,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Supplemental disclosure with respect to cash flows</t>
+          <t>CASH FLOWS FROM (USED IN) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Interest paid in cash $</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>Increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="5" t="n">
+        <v>0.288288</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>-0.037775</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17322,29 +17234,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Supplemental disclosure with respect to cash flows</t>
+          <t>CASH FLOWS FROM (USED IN) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Income tax paid in cash $</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="5" t="n">
+        <v>0.058349</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.346637</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17415,25 +17327,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>From May 25,</t>
+          <t>CASH FLOWS FROM (USED IN) FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2011 October</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" s="5" t="n">
-        <v>0.00201</v>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.346637</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.308862</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17504,24 +17420,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CASH FLOWS (USED IN) OPERATING ACTIVITIES</t>
+          <t>Supplemental disclosure with respect to cash flows</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="n">
-        <v>-0.020967</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>-0.073493</v>
+          <t>Interest paid in cash $</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -17597,26 +17513,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Supplemental disclosure with respect to cash flows</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Income tax paid in cash $</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F112" s="5" t="n">
-        <v>0.03394</v>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -17692,24 +17606,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>From May 25,</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Decrease (increase) in accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>2011 October</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" s="5" t="n">
-        <v>0.006601</v>
+        <v>0.00201</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>-3e-06</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -17785,22 +17695,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ACTIVITIES</t>
+          <t>CASH FLOWS (USED IN) OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Deferred charges</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
-        <v>-0.02529</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.020967</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>-0.073493</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -17876,24 +17788,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ACTIVITIES</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Issuance of common shares</t>
+          <t>Stock based compensation</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="n">
-        <v>0.1</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>0.39161</v>
+        <v>0.03394</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -17969,26 +17883,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ACTIVITIES</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Agent’s options exercise for issuance of common shares</t>
+          <t>Decrease (increase) in accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0.006601</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.0203</v>
+        <v>-3e-06</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -18069,21 +17981,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>-0.075292</v>
+          <t>Deferred charges</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>-0.02529</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -18164,19 +18072,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Net cash flows provided by financing activities</t>
+          <t>Issuance of common shares</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0.07471</v>
+        <v>0.1</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0.336618</v>
+        <v>0.39161</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -18257,19 +18165,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
+          <t>Agent’s options exercise for issuance of common shares</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>0.058349</v>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>0.288288</v>
+        <v>0.0203</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -18350,12 +18260,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -18364,7 +18274,7 @@
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.058349</v>
+        <v>-0.075292</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -18445,19 +18355,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
+          <t>Net cash flows provided by financing activities</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0.058349</v>
+        <v>0.07471</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0.346637</v>
+        <v>0.336618</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -18528,25 +18438,29 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>October 31, 2025 October</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in cash</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>0.058349</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.288288</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -18603,110 +18517,138 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R122" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="S122" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>ACTIVITIES</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Audit and accounting fees $</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" s="5" t="n">
-        <v>0.005</v>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0.009860000000000001</v>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>0.0195</v>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>0.03861</v>
+        <v>0.058349</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J123" s="5" t="n">
-        <v>0.0107</v>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>0.0107</v>
-      </c>
-      <c r="L123" s="5" t="n">
-        <v>0.01163</v>
-      </c>
-      <c r="M123" s="5" t="n">
-        <v>0.01484</v>
-      </c>
-      <c r="N123" s="5" t="n">
-        <v>0.014867</v>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P123" s="5" t="n">
-        <v>0.0117</v>
-      </c>
-      <c r="Q123" s="5" t="n">
-        <v>0.01242</v>
-      </c>
-      <c r="R123" s="5" t="n">
-        <v>0.017171</v>
-      </c>
-      <c r="S123" s="5" t="n">
-        <v>0.014617</v>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>ACTIVITIES</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Management fees (Note 8)</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>0.058349</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>0.346637</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -18753,17 +18695,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P124" s="5" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="Q124" s="5" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="R124" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="S124" s="5" t="n">
-        <v>0.015</v>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -18772,65 +18722,83 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Office expenses</t>
+          <t>October 31, 2025 October</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" s="5" t="n">
-        <v>0.002605</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>0.002768</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>0.000987</v>
-      </c>
-      <c r="H125" s="5" t="n">
-        <v>0.00277</v>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J125" s="5" t="n">
-        <v>0.00328</v>
-      </c>
-      <c r="K125" s="5" t="n">
-        <v>0.008439</v>
-      </c>
-      <c r="L125" s="5" t="n">
-        <v>0.003752</v>
-      </c>
-      <c r="M125" s="5" t="n">
-        <v>0.001987</v>
-      </c>
-      <c r="N125" s="5" t="n">
-        <v>0.002198</v>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P125" s="5" t="n">
-        <v>0.002104</v>
-      </c>
-      <c r="Q125" s="5" t="n">
-        <v>0.002142</v>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R125" s="5" t="n">
-        <v>0.002375</v>
+        <v>0.002024</v>
       </c>
       <c r="S125" s="5" t="n">
-        <v>0.00237</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="126">
@@ -18846,62 +18814,54 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Stock transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Audit and accounting fees $</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" s="5" t="n">
-        <v>0.001135</v>
+        <v>0.005</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.006284</v>
+        <v>0.009860000000000001</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.01796</v>
+        <v>0.0195</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>0.031192</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03861</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>0.02498</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>0.016208</v>
+        <v>0.0107</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>0.014702</v>
+        <v>0.0107</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>0.013929</v>
+        <v>0.01163</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.007912000000000001</v>
+        <v>0.01484</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>0.010612</v>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014867</v>
+      </c>
+      <c r="O126" s="5" t="n">
+        <v>0.0127</v>
       </c>
       <c r="P126" s="5" t="n">
-        <v>0.009776999999999999</v>
+        <v>0.0117</v>
       </c>
       <c r="Q126" s="5" t="n">
-        <v>0.012248</v>
+        <v>0.01242</v>
       </c>
       <c r="R126" s="5" t="n">
-        <v>0.008558</v>
+        <v>0.017171</v>
       </c>
       <c r="S126" s="5" t="n">
-        <v>0.007953</v>
+        <v>0.014617</v>
       </c>
     </row>
     <row r="127">
@@ -18917,36 +18877,48 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Total Operating Expenses</t>
+          <t>Management fees (Note 8)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>0.020967</v>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>0.073602</v>
-      </c>
-      <c r="G127" s="5" t="n">
-        <v>0.054941</v>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>0.139262</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J127" s="5" t="n">
-        <v>0.056844</v>
-      </c>
-      <c r="K127" s="5" t="n">
-        <v>0.09148100000000001</v>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -18963,26 +18935,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O127" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="P127" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Q127" s="5" t="n">
+        <v>0.014</v>
       </c>
       <c r="R127" s="5" t="n">
-        <v>0.043104</v>
+        <v>0.015</v>
       </c>
       <c r="S127" s="5" t="n">
-        <v>0.03994</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="128">
@@ -18998,72 +18964,58 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
+          <t>Office expenses</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0.002605</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>0.002768</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.000987</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>0.01077</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>0.013636</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>0.00328</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>-0.09148100000000001</v>
+        <v>0.008439</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>-0.159978</v>
+        <v>0.003752</v>
       </c>
       <c r="M128" s="5" t="n">
-        <v>-0.102701</v>
+        <v>0.001987</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>-0.045603</v>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002198</v>
+      </c>
+      <c r="O128" s="5" t="n">
+        <v>0.002107</v>
       </c>
       <c r="P128" s="5" t="n">
-        <v>-0.037651</v>
+        <v>0.002104</v>
       </c>
       <c r="Q128" s="5" t="n">
-        <v>-0.041697</v>
+        <v>0.002142</v>
       </c>
       <c r="R128" s="5" t="n">
-        <v>-0.043104</v>
+        <v>0.002375</v>
       </c>
       <c r="S128" s="5" t="n">
-        <v>-0.03994</v>
+        <v>0.00237</v>
       </c>
     </row>
     <row r="129">
@@ -19079,84 +19031,58 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
+          <t>Stock transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0.001135</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>0.006284</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.01796</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>0.031192</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>0.018142</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>0.016208</v>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>0.014702</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>0.013929</v>
+      </c>
+      <c r="M129" s="5" t="n">
+        <v>0.007912000000000001</v>
+      </c>
+      <c r="N129" s="5" t="n">
+        <v>0.010612</v>
+      </c>
+      <c r="O129" s="5" t="n">
+        <v>0.009702000000000001</v>
+      </c>
+      <c r="P129" s="5" t="n">
+        <v>0.009776999999999999</v>
+      </c>
+      <c r="Q129" s="5" t="n">
+        <v>0.012248</v>
       </c>
       <c r="R129" s="5" t="n">
-        <v>-5e-09</v>
+        <v>0.008558</v>
       </c>
       <c r="S129" s="5" t="n">
-        <v>-4e-09</v>
+        <v>0.007953</v>
       </c>
     </row>
     <row r="130">
@@ -19167,49 +19093,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>0.020967</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>0.073602</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.054941</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>0.139262</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>0.09288200000000001</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>0.056844</v>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>0.09148100000000001</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -19242,10 +19158,10 @@
         </is>
       </c>
       <c r="R130" s="5" t="n">
-        <v>9.5341</v>
+        <v>0.043104</v>
       </c>
       <c r="S130" s="5" t="n">
-        <v>9.5341</v>
+        <v>0.03994</v>
       </c>
     </row>
     <row r="131">
@@ -19254,13 +19170,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>October 31, 2024 October</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -19291,46 +19215,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K131" s="5" t="n">
+        <v>-0.09148100000000001</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>-0.159978</v>
+      </c>
+      <c r="M131" s="5" t="n">
+        <v>-0.102701</v>
+      </c>
+      <c r="N131" s="5" t="n">
+        <v>-0.045603</v>
+      </c>
+      <c r="O131" s="5" t="n">
+        <v>-0.038509</v>
+      </c>
+      <c r="P131" s="5" t="n">
+        <v>-0.037651</v>
       </c>
       <c r="Q131" s="5" t="n">
-        <v>0.002023</v>
+        <v>-0.041697</v>
       </c>
       <c r="R131" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.043104</v>
+      </c>
+      <c r="S131" s="5" t="n">
+        <v>-0.03994</v>
       </c>
     </row>
     <row r="132">
@@ -19346,45 +19256,63 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Loss per share - basic and diluted $</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="F132" s="5" t="n">
-        <v>0.00275</v>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>0.016494</v>
-      </c>
-      <c r="H132" s="5" t="n">
-        <v>0.031172</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J132" s="5" t="n">
-        <v>0.010556</v>
-      </c>
-      <c r="K132" s="5" t="n">
-        <v>0.008443000000000001</v>
-      </c>
-      <c r="L132" s="5" t="n">
-        <v>0.006941</v>
-      </c>
-      <c r="M132" s="5" t="n">
-        <v>0.010937</v>
-      </c>
-      <c r="N132" s="5" t="n">
-        <v>0.003926</v>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -19396,18 +19324,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q132" s="5" t="n">
-        <v>0.000887</v>
-      </c>
-      <c r="R132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R132" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="S132" s="5" t="n">
+        <v>-4e-09</v>
       </c>
     </row>
     <row r="133">
@@ -19418,19 +19344,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Total Operating Expense</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -19486,19 +19408,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P133" s="5" t="n">
-        <v>0.037651</v>
-      </c>
-      <c r="Q133" s="5" t="n">
-        <v>0.041697</v>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R133" s="5" t="n">
-        <v>0.043104</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.5341</v>
+      </c>
+      <c r="S133" s="5" t="n">
+        <v>9.5341</v>
       </c>
     </row>
     <row r="134">
@@ -19507,21 +19431,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Loss per share- basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>October 31, 2024 October</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -19552,31 +19468,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K134" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="L134" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="M134" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="N134" s="5" t="n">
-        <v>0</v>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P134" s="5" t="n">
-        <v>0</v>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q134" s="5" t="n">
-        <v>-4e-09</v>
+        <v>0.002023</v>
       </c>
       <c r="R134" s="5" t="n">
-        <v>-5e-09</v>
+        <v>3.1e-05</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -19592,68 +19518,66 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding- basic and diluted</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.016494</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>0.031172</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0.019738</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>8.817852999999999</v>
+        <v>0.010556</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>8.943415</v>
+        <v>0.008443000000000001</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>9.258552</v>
+        <v>0.006941</v>
       </c>
       <c r="M135" s="5" t="n">
-        <v>9.491263999999999</v>
+        <v>0.010937</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>9.491263999999999</v>
+        <v>0.003926</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P135" s="5" t="n">
-        <v>9.5341</v>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q135" s="5" t="n">
-        <v>9.5341</v>
-      </c>
-      <c r="R135" s="5" t="n">
-        <v>9.5341</v>
+        <v>0.000887</v>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -19667,13 +19591,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>October 31, 2023 October</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
+          <t>Total Operating Expense</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -19730,15 +19662,13 @@
         </is>
       </c>
       <c r="P136" s="5" t="n">
-        <v>0.002022</v>
+        <v>0.037651</v>
       </c>
       <c r="Q136" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.041697</v>
+      </c>
+      <c r="R136" s="5" t="n">
+        <v>0.043104</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -19752,13 +19682,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>October 31, 2019 October</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>Loss per share- basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -19789,41 +19727,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K137" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>0.002018</v>
+        <v>-1e-08</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="5" t="n">
+        <v>-4e-09</v>
+      </c>
+      <c r="R137" s="5" t="n">
+        <v>-5e-09</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -19839,12 +19765,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Finder’s fee (Note 7)</t>
+          <t>Weighted average number of common shares outstanding- basic and diluted</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -19863,52 +19789,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H138" s="5" t="n">
+        <v>6.9171</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>6.950853</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>8.817852999999999</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>8.943415</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>0.00125</v>
+        <v>9.258552</v>
       </c>
       <c r="M138" s="5" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.491263999999999</v>
+      </c>
+      <c r="N138" s="5" t="n">
+        <v>9.491263999999999</v>
+      </c>
+      <c r="O138" s="5" t="n">
+        <v>9.5341</v>
+      </c>
+      <c r="P138" s="5" t="n">
+        <v>9.5341</v>
+      </c>
+      <c r="Q138" s="5" t="n">
+        <v>9.5341</v>
+      </c>
+      <c r="R138" s="5" t="n">
+        <v>9.5341</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -19922,21 +19834,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Management fees (Note 9)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>October 31, 2023 October</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -19962,35 +19866,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J139" s="5" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="K139" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L139" s="5" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="M139" s="5" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="N139" s="5" t="n">
-        <v>0.014</v>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P139" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="Q139" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="R139" t="inlineStr">
         <is>
@@ -20009,14 +19919,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Property investigation (Note 7)</t>
+          <t>October 31, 2019 October</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -20055,16 +19961,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L140" s="5" t="n">
-        <v>0.069089</v>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M140" s="5" t="n">
-        <v>0.052125</v>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002018</v>
+      </c>
+      <c r="N140" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -20098,10 +20004,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>October 31, 2018 October</t>
+          <t>Finder’s fee (Note 7)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -20120,31 +20030,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H141" s="5" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>0.008999999999999999</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>0.002017</v>
+        <v>0.00125</v>
       </c>
       <c r="M141" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.0009</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
@@ -20190,10 +20092,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Payroll expense (Note 9)</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>Management fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -20209,38 +20115,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H142" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="J142" s="5" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>0.039387</v>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014</v>
+      </c>
+      <c r="M142" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="N142" s="5" t="n">
+        <v>0.014</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -20274,10 +20168,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>October 31, 2017 October</t>
+          <t>Property investigation (Note 7)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -20311,16 +20209,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K143" s="5" t="n">
-        <v>0.002016</v>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L143" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.069089</v>
+      </c>
+      <c r="M143" s="5" t="n">
+        <v>0.052125</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -20359,14 +20257,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Property Investigation (Note 7)</t>
+          <t>October 31, 2018 October</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -20400,16 +20294,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K144" s="5" t="n">
-        <v>0.0113</v>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L144" s="5" t="n">
-        <v>0.069089</v>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002017</v>
+      </c>
+      <c r="M144" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
@@ -20455,7 +20349,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Share-based Compensation (Note 8(c))</t>
+          <t>Payroll expense (Note 9)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -20489,13 +20383,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K145" s="5" t="n">
-        <v>0.008897</v>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>0.039387</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -20542,7 +20436,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>October 31, 2016 October</t>
+          <t>October 31, 2017 October</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -20571,16 +20465,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J146" s="5" t="n">
-        <v>0.002015</v>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K146" s="5" t="n">
+        <v>0.002016</v>
+      </c>
+      <c r="L146" s="5" t="n">
         <v>3.1e-05</v>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -20626,12 +20520,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets</t>
+          <t>Property Investigation (Note 7)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -20660,18 +20554,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J147" s="5" t="n">
-        <v>-0.046</v>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>0.069089</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -20717,19 +20609,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based Compensation (Note 8(c))</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -20755,11 +20643,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J148" s="5" t="n">
-        <v>-0.102844</v>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K148" s="5" t="n">
-        <v>-0.09148100000000001</v>
+        <v>0.008897</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -20808,21 +20698,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Loss per share- basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>October 31, 2016 October</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -20849,10 +20731,10 @@
         </is>
       </c>
       <c r="J149" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.002015</v>
       </c>
       <c r="K149" s="5" t="n">
-        <v>-1e-08</v>
+        <v>3.1e-05</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -20901,10 +20783,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>October 31, 2013 October</t>
+          <t>Impairment of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -20918,21 +20804,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G150" s="5" t="n">
-        <v>0.002012</v>
-      </c>
-      <c r="H150" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J150" s="5" t="n">
+        <v>-0.046</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -20988,15 +20876,19 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Finder’s fee</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>Net Loss and Comprehensive Loss for the Year</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -21012,23 +20904,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H151" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>-0.09288200000000001</v>
+      </c>
+      <c r="J151" s="5" t="n">
+        <v>-0.102844</v>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>-0.09148100000000001</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -21079,17 +20967,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Management fees</t>
+          <t>Loss per share- basic and diluted $</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -21107,23 +20995,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H152" s="5" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="J152" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -21179,7 +21063,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Property Investigation fees</t>
+          <t>Stock based payment (Note 8d)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -21199,12 +21083,10 @@
         </is>
       </c>
       <c r="H153" s="5" t="n">
-        <v>0.002822</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016196</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>0.002386</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -21270,7 +21152,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Stock based payment</t>
+          <t>Property Investigation fees</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -21279,8 +21161,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F154" s="5" t="n">
-        <v>0.03394</v>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -21288,7 +21172,7 @@
         </is>
       </c>
       <c r="H154" s="5" t="n">
-        <v>0.016196</v>
+        <v>0.002822</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -21472,10 +21356,8 @@
       <c r="H156" s="5" t="n">
         <v>-0.139259</v>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I156" s="5" t="n">
+        <v>-0.09288200000000001</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -21565,10 +21447,8 @@
       <c r="H157" s="5" t="n">
         <v>-2e-08</v>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I157" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -21630,7 +21510,7 @@
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>October 31, 2012 October</t>
+          <t>October 31, 2013 October</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -21639,16 +21519,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F158" s="5" t="n">
-        <v>0.002011</v>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G158" s="5" t="n">
+        <v>0.002012</v>
+      </c>
+      <c r="H158" s="5" t="n">
         <v>3.1e-05</v>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -21719,31 +21599,27 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Finder’s fee</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F159" s="5" t="n">
-        <v>0.018</v>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H159" s="5" t="n">
+        <v>0.0035</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -21809,30 +21685,36 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DEFICIT, BEGINNING OF THE YEAR</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>Management fees</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F160" s="5" t="n">
-        <v>-0.020967</v>
-      </c>
-      <c r="G160" s="5" t="n">
-        <v>-0.09446</v>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>0.013</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -21898,12 +21780,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>DEFICIT, END OF THE YEAR $</t>
+          <t>Stock based payment</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -21913,15 +21795,15 @@
         </is>
       </c>
       <c r="F161" s="5" t="n">
-        <v>-0.09446</v>
-      </c>
-      <c r="G161" s="5" t="n">
-        <v>-0.149399</v>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03394</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>0.016196</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -21985,29 +21867,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="n">
-        <v>-1e-08</v>
+          <t>October 31, 2012 October</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.002011</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>-1e-08</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -22078,25 +21954,31 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>of Shares         Capital             Reserves            Deficit              Total</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Balance November 1, 2010 2,000,000 $ 100,000 $ - $</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>0.07903300000000001</v>
-      </c>
-      <c r="G163" s="5" t="n">
-        <v>-0.020967</v>
+        <v>0.018</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -22167,12 +22049,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Share issuance for cash</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Share issuance for cash</t>
+          <t>DEFICIT, BEGINNING OF THE YEAR</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -22182,12 +22064,10 @@
         </is>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.39161</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.020967</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>-0.09446</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -22258,12 +22138,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>at $0.10 per share</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Share issuance cost</t>
+          <t>DEFICIT, END OF THE YEAR $</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -22273,10 +22153,10 @@
         </is>
       </c>
       <c r="F165" s="5" t="n">
-        <v>-0.126502</v>
+        <v>-0.09446</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>-0.126502</v>
+        <v>-0.149399</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -22347,27 +22227,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>at $0.10 per share</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Agent’s options 203,000 33,749 12,471</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>0.04622</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -22438,12 +22318,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Stock options granted to</t>
+          <t>of Shares         Capital             Reserves            Deficit              Total</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Stock options granted to</t>
+          <t>Balance November 1, 2010 2,000,000 $ 100,000 $ - $</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -22453,12 +22333,10 @@
         </is>
       </c>
       <c r="F167" s="5" t="n">
-        <v>0.03394</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07903300000000001</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>-0.020967</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -22529,29 +22407,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>officers and directors</t>
+          <t>Share issuance for cash</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issuance for cash</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F168" s="5" t="n">
-        <v>-0.073493</v>
-      </c>
-      <c r="G168" s="5" t="n">
-        <v>-0.073493</v>
+        <v>0.39161</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -22622,12 +22498,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>officers and directors</t>
+          <t>at $0.10 per share</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Balance, October 31, 2011 6,119,100 398,857 46,411</t>
+          <t>Share issuance cost</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -22637,10 +22513,10 @@
         </is>
       </c>
       <c r="F169" s="5" t="n">
-        <v>0.350808</v>
+        <v>-0.126502</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>-0.09446</v>
+        <v>-0.126502</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -22711,12 +22587,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>officers and directors</t>
+          <t>at $0.10 per share</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Balance, October 31, 2012 6,119,100 $ 398,857 $ 46,411 $</t>
+          <t>Agent’s options 203,000 33,749 12,471</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -22726,10 +22602,12 @@
         </is>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.295869</v>
-      </c>
-      <c r="G170" s="5" t="n">
-        <v>-0.149399</v>
+        <v>0.04622</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -22798,18 +22676,24 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Stock options granted to</t>
+        </is>
+      </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Year Ended From May</t>
+          <t>Stock options granted to</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" s="5" t="n">
-        <v>0.00201</v>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F171" s="5" t="n">
-        <v>2.5e-05</v>
+        <v>0.03394</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -22883,23 +22767,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>officers and directors</t>
+        </is>
+      </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2011 to October</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" s="5" t="n">
-        <v>0.00201</v>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F172" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.073493</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>-0.073493</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -22970,27 +22862,25 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>officers and directors</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Travel expenses</t>
+          <t>Balance, October 31, 2011 6,119,100 398,857 46,411</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" s="5" t="n">
-        <v>0.003727</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>0.350808</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>-0.09446</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -23061,12 +22951,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>officers and directors</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
+          <t>Balance, October 31, 2012 6,119,100 $ 398,857 $ 46,411 $</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -23076,12 +22966,10 @@
         </is>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.03394</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.295869</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>-0.149399</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -23150,26 +23038,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Year Ended From May</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" s="5" t="n">
-        <v>-0.020967</v>
+        <v>0.00201</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>-0.073493</v>
+        <v>2.5e-05</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -23243,24 +23123,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
+      <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Deficit, beginning of period</t>
+          <t>2011 to October</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E176" s="5" t="n">
+        <v>0.00201</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>-0.020967</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -23336,82 +23210,448 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>outstanding</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>– basic and diluted</t>
+          <t>Travel expenses</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" s="5" t="n">
+        <v>0.003727</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Stock based compensation</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>0.03394</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="n">
+        <v>-0.020967</v>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>-0.073493</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of period</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>-0.020967</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>– basic and diluted</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F177" s="5" t="n">
+      <c r="F181" s="5" t="n">
         <v>4.366416</v>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S177" t="inlineStr">
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
